--- a/EXCEL/class notes/day5 data validation/Data Validation Indirect.xlsx
+++ b/EXCEL/class notes/day5 data validation/Data Validation Indirect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day5 data validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F456A5D-FDF5-4E16-A477-6B823B5709ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A500AC08-C9C3-49A1-BA81-6EC89821CD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{FD4623A8-ED0C-4945-9D3A-E5812CE5A0DC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{FD4623A8-ED0C-4945-9D3A-E5812CE5A0DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Data validation Indirect (2)" sheetId="5" r:id="rId1"/>
@@ -40,8 +40,39 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -799,28 +830,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{398786DF-06B9-4EC2-A841-AC8DE8A86FA4}">
-  <dimension ref="B1:K19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:K21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="I3" t="str">
         <f>C5</f>
         <v>Application form new</v>
@@ -830,8 +861,8 @@
         <v>Application form new</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
       <c r="C5" s="13" t="s">
         <v>69</v>
@@ -849,7 +880,7 @@
         <v>$C$5</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="15"/>
       <c r="D6" s="16"/>
       <c r="F6" s="24" t="s">
@@ -859,7 +890,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
         <v>0</v>
       </c>
@@ -870,11 +901,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="15"/>
       <c r="D8" s="16"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="s">
         <v>55</v>
       </c>
@@ -883,7 +914,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="15"/>
       <c r="D10" s="16"/>
       <c r="K10" t="str">
@@ -891,7 +922,7 @@
         <v>Application form new</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
@@ -905,16 +936,16 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="15"/>
       <c r="D12" s="16"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="15" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>59</v>
@@ -929,7 +960,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="15"/>
       <c r="D14" s="16"/>
       <c r="F14" s="6" t="s">
@@ -942,12 +973,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>5</v>
@@ -959,14 +990,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="15"/>
       <c r="D16" s="16"/>
       <c r="F16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
         <v>2</v>
       </c>
@@ -974,14 +1005,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="19"/>
       <c r="C18" s="20"/>
       <c r="D18" s="21"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="I21" t="str" cm="1">
+        <f t="array" aca="1" ref="I21" ca="1">INDIRECT(K5)</f>
+        <v>Application form new</v>
       </c>
     </row>
   </sheetData>
@@ -1015,33 +1052,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD5A387-369F-40D3-8F5E-D6A7F5CA82CF}">
   <dimension ref="B1:K19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:11" x14ac:dyDescent="0.3">
       <c r="F1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K3">
         <f>C6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
       <c r="C5" s="13" t="s">
         <v>49</v>
@@ -1055,7 +1092,7 @@
         <v>$B$5</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="15"/>
       <c r="D6" s="16"/>
       <c r="F6" s="5" t="s">
@@ -1065,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
         <v>0</v>
       </c>
@@ -1076,11 +1113,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="15"/>
       <c r="D8" s="16"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="15" t="s">
         <v>55</v>
       </c>
@@ -1091,11 +1128,11 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="15"/>
       <c r="D10" s="16"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
@@ -1103,16 +1140,16 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="15"/>
       <c r="D12" s="16"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="15" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>59</v>
@@ -1128,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="15"/>
       <c r="D14" s="16"/>
       <c r="F14" t="s">
@@ -1144,12 +1181,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
@@ -1161,27 +1198,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="15"/>
       <c r="D16" s="16"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="19"/>
       <c r="C18" s="20"/>
       <c r="D18" s="21"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>53</v>
       </c>
@@ -1217,14 +1254,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D10458DF-D842-435C-9E78-E87FFC06A18C}">
   <dimension ref="C5:I15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C5" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1241,7 +1278,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
@@ -1258,7 +1295,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1275,7 +1312,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
@@ -1292,17 +1329,17 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C13" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C15" s="5" t="s">
         <v>12</v>
       </c>
@@ -1314,7 +1351,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13" xr:uid="{066193FF-8FC3-4E14-A6F6-3032A6E05A87}">
       <formula1>$C$6:$C$9</formula1>
     </dataValidation>
@@ -1329,13 +1366,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB400ADE-5602-40FA-9C8C-489C61B05B02}">
   <dimension ref="A1:U16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="15" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
@@ -1349,7 +1386,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1001</v>
       </c>
@@ -1364,7 +1401,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1002</v>
       </c>
@@ -1427,7 +1464,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1003</v>
       </c>
@@ -1505,7 +1542,7 @@
         <v>Ram15</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1004</v>
       </c>
@@ -1583,7 +1620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1005</v>
       </c>
@@ -1598,7 +1635,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1006</v>
       </c>
@@ -1613,7 +1650,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1007</v>
       </c>
@@ -1631,7 +1668,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1008</v>
       </c>
@@ -1646,7 +1683,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>1009</v>
       </c>
@@ -1661,7 +1698,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>1010</v>
       </c>
@@ -1676,7 +1713,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1011</v>
       </c>
@@ -1691,7 +1728,7 @@
         <v>Fail</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>1012</v>
       </c>
@@ -1706,7 +1743,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1013</v>
       </c>
@@ -1721,7 +1758,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>1014</v>
       </c>
@@ -1736,7 +1773,7 @@
         <v>Pass</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>1015</v>
       </c>
@@ -1761,9 +1798,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA18C577-5635-4DA2-ACE4-62B3F2106718}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>12</v>
       </c>
@@ -1774,7 +1811,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1001</v>
       </c>
@@ -1791,7 +1828,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1002</v>
       </c>
@@ -1802,7 +1839,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1003</v>
       </c>
@@ -1816,16 +1853,16 @@
         <v>12</v>
       </c>
       <c r="G4" s="7">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="J4" s="7">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1004</v>
       </c>
@@ -1840,17 +1877,17 @@
       </c>
       <c r="G5" s="8" t="str">
         <f>VLOOKUP(ID,_xlnm.Database,2,0)</f>
-        <v>Ram14</v>
+        <v>Ram2</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>0</v>
       </c>
       <c r="J5" s="8" t="str">
         <f>VLOOKUP($J$4,$A$1:$C$16,2,0)</f>
-        <v>Ram5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+        <v>Ram1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>1005</v>
       </c>
@@ -1865,20 +1902,20 @@
       </c>
       <c r="G6" s="8">
         <f>VLOOKUP(ID,_xlnm.Database,3,0)</f>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J6" s="8">
         <f>VLOOKUP($J$4,$A$1:$C$16,3,0)</f>
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="M6" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1006</v>
       </c>
@@ -1892,7 +1929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1007</v>
       </c>
@@ -1906,7 +1943,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1008</v>
       </c>
@@ -1920,7 +1957,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>1009</v>
       </c>
@@ -1931,7 +1968,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>1010</v>
       </c>
@@ -1942,7 +1979,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1011</v>
       </c>
@@ -1957,7 +1994,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>1012</v>
       </c>
@@ -1971,7 +2008,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1013</v>
       </c>
@@ -1982,7 +2019,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>1014</v>
       </c>
@@ -1993,7 +2030,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>1015</v>
       </c>
